--- a/IMRADS/TALISAY/Distances/shel_shel_distance_matrix.xlsx
+++ b/IMRADS/TALISAY/Distances/shel_shel_distance_matrix.xlsx
@@ -1,49 +1,55 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24326"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PERSONAL\BRYAN\bulsu\Thesis 1\ShelterAlloc_Thesis\IMRADS\TALISAY\Distances\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8CA26F9-D76B-4A08-8AAC-C0B70E181FB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="2616" yWindow="2616" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="11">
   <si>
-    <t>San Fernado Brgy. Hall</t>
-  </si>
-  <si>
-    <t>SantaClara Brgy. Hall</t>
-  </si>
-  <si>
-    <t>Darasa Brgy. Hall</t>
-  </si>
-  <si>
-    <t>San Antonio Brgy. Hall</t>
-  </si>
-  <si>
-    <t>Tagaytay Unida Church</t>
-  </si>
-  <si>
-    <t>Maugat Gymnasium</t>
-  </si>
-  <si>
-    <t>Brgy.San Jose BB Court</t>
-  </si>
-  <si>
-    <t>Suplang Covered Court</t>
-  </si>
-  <si>
-    <t>City EC of Sto. Tomas</t>
-  </si>
-  <si>
-    <t>Brgy. Asis-3 EC</t>
+    <t>PEDRO ALEGRE AURE SENIORHIGH SCHOOL</t>
+  </si>
+  <si>
+    <t>SILANG JUNCTION SOUTH</t>
+  </si>
+  <si>
+    <t>SUPLANG</t>
+  </si>
+  <si>
+    <t>LUYOS</t>
+  </si>
+  <si>
+    <t>DAYAPAN ELEMENTARY SCHOOL</t>
+  </si>
+  <si>
+    <t>SAMBAT</t>
+  </si>
+  <si>
+    <t>TRAPICHE BASKETBALL COURT</t>
+  </si>
+  <si>
+    <t>TINURIK</t>
+  </si>
+  <si>
+    <t>POBLACION</t>
+  </si>
+  <si>
+    <t>SANTA CLARA</t>
   </si>
   <si>
     <t>Shelters</t>
@@ -52,8 +58,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -105,17 +111,26 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -162,7 +177,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -194,9 +209,27 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -228,6 +261,24 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -403,11 +454,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -442,353 +493,353 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2">
-        <v>0</v>
-      </c>
-      <c r="C2">
-        <v>39.39843800000001</v>
-      </c>
-      <c r="D2">
-        <v>10.582127</v>
-      </c>
-      <c r="E2">
-        <v>37.637885</v>
-      </c>
-      <c r="F2">
-        <v>32.92291700000001</v>
-      </c>
-      <c r="G2">
-        <v>78.55604399999989</v>
-      </c>
-      <c r="H2">
-        <v>41.192638</v>
-      </c>
-      <c r="I2">
-        <v>24.11819299999998</v>
-      </c>
-      <c r="J2">
-        <v>13.007935</v>
-      </c>
-      <c r="K2">
-        <v>46.93167699999998</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
+      <c r="B2" s="2">
+        <v>0</v>
+      </c>
+      <c r="C2" s="2">
+        <v>7.545535000000001</v>
+      </c>
+      <c r="D2" s="2">
+        <v>28.384357999999981</v>
+      </c>
+      <c r="E2" s="2">
+        <v>25.66362399999996</v>
+      </c>
+      <c r="F2" s="2">
+        <v>25.526992999999969</v>
+      </c>
+      <c r="G2" s="2">
+        <v>32.084949999999978</v>
+      </c>
+      <c r="H2" s="2">
+        <v>32.236956999999983</v>
+      </c>
+      <c r="I2" s="2">
+        <v>33.814754999999991</v>
+      </c>
+      <c r="J2" s="2">
+        <v>38.620220000000018</v>
+      </c>
+      <c r="K2" s="2">
+        <v>45.157207</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3">
-        <v>39.39843800000001</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3">
-        <v>40.60795500000002</v>
-      </c>
-      <c r="E3">
-        <v>17.843377</v>
-      </c>
-      <c r="F3">
-        <v>54.16611400000004</v>
-      </c>
-      <c r="G3">
-        <v>67.35856200000005</v>
-      </c>
-      <c r="H3">
-        <v>15.536631</v>
-      </c>
-      <c r="I3">
-        <v>54.98515900000006</v>
-      </c>
-      <c r="J3">
-        <v>45.81810200000007</v>
-      </c>
-      <c r="K3">
-        <v>57.38982400000003</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
+      <c r="B3" s="2">
+        <v>7.545535000000001</v>
+      </c>
+      <c r="C3" s="2">
+        <v>0</v>
+      </c>
+      <c r="D3" s="2">
+        <v>23.124230000000001</v>
+      </c>
+      <c r="E3" s="2">
+        <v>20.403495999999969</v>
+      </c>
+      <c r="F3" s="2">
+        <v>20.266864999999971</v>
+      </c>
+      <c r="G3" s="2">
+        <v>26.82482199999999</v>
+      </c>
+      <c r="H3" s="2">
+        <v>26.976828999999999</v>
+      </c>
+      <c r="I3" s="2">
+        <v>28.554627</v>
+      </c>
+      <c r="J3" s="2">
+        <v>33.360092000000023</v>
+      </c>
+      <c r="K3" s="2">
+        <v>39.897079000000033</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B4">
-        <v>10.582127</v>
-      </c>
-      <c r="C4">
-        <v>40.607955</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="E4">
-        <v>38.84740199999998</v>
-      </c>
-      <c r="F4">
-        <v>23.02531800000001</v>
-      </c>
-      <c r="G4">
-        <v>68.65844499999986</v>
-      </c>
-      <c r="H4">
-        <v>42.83982399999999</v>
-      </c>
-      <c r="I4">
-        <v>14.87451599999999</v>
-      </c>
-      <c r="J4">
-        <v>5.210146999999999</v>
-      </c>
-      <c r="K4">
-        <v>37.03407800000005</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
+      <c r="B4" s="2">
+        <v>28.384358000000031</v>
+      </c>
+      <c r="C4" s="2">
+        <v>23.124230000000011</v>
+      </c>
+      <c r="D4" s="2">
+        <v>0</v>
+      </c>
+      <c r="E4" s="2">
+        <v>4.1986060000000007</v>
+      </c>
+      <c r="F4" s="2">
+        <v>8.0530949999999972</v>
+      </c>
+      <c r="G4" s="2">
+        <v>11.83922400000001</v>
+      </c>
+      <c r="H4" s="2">
+        <v>9.9613500000000048</v>
+      </c>
+      <c r="I4" s="2">
+        <v>14.408207000000001</v>
+      </c>
+      <c r="J4" s="2">
+        <v>17.085394000000001</v>
+      </c>
+      <c r="K4" s="2">
+        <v>23.566461</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B5">
-        <v>37.63788499999996</v>
-      </c>
-      <c r="C5">
-        <v>17.843377</v>
-      </c>
-      <c r="D5">
-        <v>38.84740199999997</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5">
-        <v>39.30804100000002</v>
-      </c>
-      <c r="G5">
-        <v>52.50048900000003</v>
-      </c>
-      <c r="H5">
-        <v>30.47480599999999</v>
-      </c>
-      <c r="I5">
-        <v>52.22318799999999</v>
-      </c>
-      <c r="J5">
-        <v>44.05754899999999</v>
-      </c>
-      <c r="K5">
-        <v>42.53175100000001</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
+      <c r="B5" s="2">
+        <v>25.66362400000002</v>
+      </c>
+      <c r="C5" s="2">
+        <v>20.403496000000001</v>
+      </c>
+      <c r="D5" s="2">
+        <v>4.1986059999999998</v>
+      </c>
+      <c r="E5" s="2">
+        <v>0</v>
+      </c>
+      <c r="F5" s="2">
+        <v>3.8544889999999992</v>
+      </c>
+      <c r="G5" s="2">
+        <v>7.883907999999999</v>
+      </c>
+      <c r="H5" s="2">
+        <v>8.0359149999999993</v>
+      </c>
+      <c r="I5" s="2">
+        <v>10.452890999999999</v>
+      </c>
+      <c r="J5" s="2">
+        <v>14.419178000000009</v>
+      </c>
+      <c r="K5" s="2">
+        <v>20.95616500000002</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B6">
-        <v>32.92291700000004</v>
-      </c>
-      <c r="C6">
-        <v>54.16611400000001</v>
-      </c>
-      <c r="D6">
-        <v>23.02531800000002</v>
-      </c>
-      <c r="E6">
-        <v>39.308041</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>47.46827499999997</v>
-      </c>
-      <c r="H6">
-        <v>60.42596900000001</v>
-      </c>
-      <c r="I6">
-        <v>16.020074</v>
-      </c>
-      <c r="J6">
-        <v>19.94592100000001</v>
-      </c>
-      <c r="K6">
-        <v>17.626992</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
+      <c r="B6" s="2">
+        <v>25.526993000000012</v>
+      </c>
+      <c r="C6" s="2">
+        <v>20.266864999999989</v>
+      </c>
+      <c r="D6" s="2">
+        <v>8.053094999999999</v>
+      </c>
+      <c r="E6" s="2">
+        <v>3.8544890000000001</v>
+      </c>
+      <c r="F6" s="2">
+        <v>0</v>
+      </c>
+      <c r="G6" s="2">
+        <v>7.7968990000000007</v>
+      </c>
+      <c r="H6" s="2">
+        <v>7.948906</v>
+      </c>
+      <c r="I6" s="2">
+        <v>10.365881999999999</v>
+      </c>
+      <c r="J6" s="2">
+        <v>14.332169</v>
+      </c>
+      <c r="K6" s="2">
+        <v>20.869156000000011</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B7">
-        <v>78.556044</v>
-      </c>
-      <c r="C7">
-        <v>67.35856199999999</v>
-      </c>
-      <c r="D7">
-        <v>68.65844500000001</v>
-      </c>
-      <c r="E7">
-        <v>52.50048900000001</v>
-      </c>
-      <c r="F7">
-        <v>47.46827499999999</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>79.98999100000003</v>
-      </c>
-      <c r="I7">
-        <v>55.29580699999998</v>
-      </c>
-      <c r="J7">
-        <v>65.55002700000001</v>
-      </c>
-      <c r="K7">
-        <v>36.92512899999998</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
+      <c r="B7" s="2">
+        <v>32.084950000000028</v>
+      </c>
+      <c r="C7" s="2">
+        <v>26.824822000000012</v>
+      </c>
+      <c r="D7" s="2">
+        <v>11.839224</v>
+      </c>
+      <c r="E7" s="2">
+        <v>7.8839079999999981</v>
+      </c>
+      <c r="F7" s="2">
+        <v>7.7968989999999989</v>
+      </c>
+      <c r="G7" s="2">
+        <v>0</v>
+      </c>
+      <c r="H7" s="2">
+        <v>2.415964999999999</v>
+      </c>
+      <c r="I7" s="2">
+        <v>3.508222</v>
+      </c>
+      <c r="J7" s="2">
+        <v>6.5352700000000006</v>
+      </c>
+      <c r="K7" s="2">
+        <v>13.072257</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B8">
-        <v>41.19263800000001</v>
-      </c>
-      <c r="C8">
-        <v>15.536631</v>
-      </c>
-      <c r="D8">
-        <v>42.83982399999999</v>
-      </c>
-      <c r="E8">
-        <v>30.47480600000002</v>
-      </c>
-      <c r="F8">
-        <v>60.42596899999997</v>
-      </c>
-      <c r="G8">
-        <v>79.9899910000001</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>57.50698600000001</v>
-      </c>
-      <c r="J8">
-        <v>48.04997099999999</v>
-      </c>
-      <c r="K8">
-        <v>70.0212530000001</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
+      <c r="B8" s="2">
+        <v>32.236957000000032</v>
+      </c>
+      <c r="C8" s="2">
+        <v>26.976829000000009</v>
+      </c>
+      <c r="D8" s="2">
+        <v>9.9613499999999959</v>
+      </c>
+      <c r="E8" s="2">
+        <v>8.0359149999999975</v>
+      </c>
+      <c r="F8" s="2">
+        <v>7.9489059999999974</v>
+      </c>
+      <c r="G8" s="2">
+        <v>2.415964999999999</v>
+      </c>
+      <c r="H8" s="2">
+        <v>0</v>
+      </c>
+      <c r="I8" s="2">
+        <v>5.6531690000000001</v>
+      </c>
+      <c r="J8" s="2">
+        <v>7.1240439999999996</v>
+      </c>
+      <c r="K8" s="2">
+        <v>13.605111000000001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B9">
-        <v>24.118193</v>
-      </c>
-      <c r="C9">
-        <v>54.98515899999995</v>
-      </c>
-      <c r="D9">
-        <v>14.874516</v>
-      </c>
-      <c r="E9">
-        <v>52.22318799999996</v>
-      </c>
-      <c r="F9">
-        <v>16.020074</v>
-      </c>
-      <c r="G9">
-        <v>55.29580699999992</v>
-      </c>
-      <c r="H9">
-        <v>57.50698600000003</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9">
-        <v>11.110258</v>
-      </c>
-      <c r="K9">
-        <v>23.67144</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
+      <c r="B9" s="2">
+        <v>33.814755000000027</v>
+      </c>
+      <c r="C9" s="2">
+        <v>28.554626999999989</v>
+      </c>
+      <c r="D9" s="2">
+        <v>14.408207000000001</v>
+      </c>
+      <c r="E9" s="2">
+        <v>10.452890999999999</v>
+      </c>
+      <c r="F9" s="2">
+        <v>10.365881999999999</v>
+      </c>
+      <c r="G9" s="2">
+        <v>3.5082220000000008</v>
+      </c>
+      <c r="H9" s="2">
+        <v>5.6531690000000001</v>
+      </c>
+      <c r="I9" s="2">
+        <v>0</v>
+      </c>
+      <c r="J9" s="2">
+        <v>7.5867769999999997</v>
+      </c>
+      <c r="K9" s="2">
+        <v>14.31607</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B10">
-        <v>13.007935</v>
-      </c>
-      <c r="C10">
-        <v>45.81810200000002</v>
-      </c>
-      <c r="D10">
-        <v>5.210147</v>
-      </c>
-      <c r="E10">
-        <v>44.05754900000002</v>
-      </c>
-      <c r="F10">
-        <v>19.945921</v>
-      </c>
-      <c r="G10">
-        <v>65.55002699999993</v>
-      </c>
-      <c r="H10">
-        <v>48.04997100000002</v>
-      </c>
-      <c r="I10">
-        <v>11.110258</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
-      <c r="K10">
-        <v>33.92566</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
+      <c r="B10" s="2">
+        <v>38.620220000000039</v>
+      </c>
+      <c r="C10" s="2">
+        <v>33.360092000000002</v>
+      </c>
+      <c r="D10" s="2">
+        <v>17.08539399999999</v>
+      </c>
+      <c r="E10" s="2">
+        <v>14.419178</v>
+      </c>
+      <c r="F10" s="2">
+        <v>14.33216899999999</v>
+      </c>
+      <c r="G10" s="2">
+        <v>6.5352700000000006</v>
+      </c>
+      <c r="H10" s="2">
+        <v>7.1240439999999996</v>
+      </c>
+      <c r="I10" s="2">
+        <v>7.5867769999999997</v>
+      </c>
+      <c r="J10" s="2">
+        <v>0</v>
+      </c>
+      <c r="K10" s="2">
+        <v>7.505783000000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B11">
-        <v>46.93167700000002</v>
-      </c>
-      <c r="C11">
-        <v>57.38982400000003</v>
-      </c>
-      <c r="D11">
-        <v>37.03407800000003</v>
-      </c>
-      <c r="E11">
-        <v>42.53175100000001</v>
-      </c>
-      <c r="F11">
-        <v>17.62699199999999</v>
-      </c>
-      <c r="G11">
-        <v>36.92512900000001</v>
-      </c>
-      <c r="H11">
-        <v>70.0212529999999</v>
-      </c>
-      <c r="I11">
-        <v>23.67143999999998</v>
-      </c>
-      <c r="J11">
-        <v>33.92566</v>
-      </c>
-      <c r="K11">
+      <c r="B11" s="2">
+        <v>45.157207000000056</v>
+      </c>
+      <c r="C11" s="2">
+        <v>39.897079000000012</v>
+      </c>
+      <c r="D11" s="2">
+        <v>23.566460999999979</v>
+      </c>
+      <c r="E11" s="2">
+        <v>20.956164999999981</v>
+      </c>
+      <c r="F11" s="2">
+        <v>20.869155999999979</v>
+      </c>
+      <c r="G11" s="2">
+        <v>13.072257</v>
+      </c>
+      <c r="H11" s="2">
+        <v>13.605111000000001</v>
+      </c>
+      <c r="I11" s="2">
+        <v>14.31607</v>
+      </c>
+      <c r="J11" s="2">
+        <v>7.5057829999999992</v>
+      </c>
+      <c r="K11" s="2">
         <v>0</v>
       </c>
     </row>
